--- a/backend/data/attachments/risk_流动性风险监测报告_3.xlsx
+++ b/backend/data/attachments/risk_流动性风险监测报告_3.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trust-357</t>
+          <t>Trust-610</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20108</v>
+        <v>24127</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -464,12 +464,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,25 +481,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trust-296</t>
+          <t>Trust-567</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19180</v>
+        <v>41127</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -511,11 +511,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trust-202</t>
+          <t>Trust-984</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17721</v>
+        <v>9575</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -541,15 +541,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trust-114</t>
+          <t>Trust-940</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40005</v>
+        <v>5168</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -559,23 +559,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trust-814</t>
+          <t>Trust-986</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13275</v>
+        <v>14738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -584,42 +584,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trust-580</t>
+          <t>Trust-566</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36373</v>
+        <v>26088</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -631,11 +631,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trust-982</t>
+          <t>Trust-976</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36308</v>
+        <v>31920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -644,42 +644,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trust-690</t>
+          <t>Trust-495</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46251</v>
+        <v>48495</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
